--- a/hpi_scraper/JobsHiring/coresignal/coresignal_data.xlsx
+++ b/hpi_scraper/JobsHiring/coresignal/coresignal_data.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -506,47 +506,47 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>eng: 2; design: 0; it: 3; sales: 0; ops: 0</t>
+          <t>eng: 4; design: 0; it: 0; sales: 0; ops: 0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA; Seattle, WA; Singapore, Singapore; Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
+          <t>Singapore, Singapore; Jakarta, Indonesia; São Paulo, Brazil; Singapore</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b94aaec968b170; http://www.indeed.com/job/global-marketing-manager-93b94aaec968b170; https://www.indeed.com/viewjob?jk=45ae33a096b7eda1; http://www.indeed.com/job/global-marketing-manager-45ae33a096b7eda1; https://www.linkedin.com/jobs/view/associate-finance-accounting-credit-management-at-singtel-4231791741; https://groupcareers.singtel.com/job/Associate-Finance-&amp;-Accounting-%28Credit-Management%29-Sing/1065325766/; https://www.linkedin.com/jobs/view/lead-data-scientist-%23aida-at-singtel-4298144986; https://groupcareers.singtel.com/job/Senior-Data-Scientist-AIDA-Sing/1214874366/; https://www.linkedin.com/jobs/view/director-senior-director-technology-digitalization-global-business-services-at-singtel-4292959990; https://groupcareers.singtel.com/job/DirectorSenior-Director%2C-Technology-&amp;-Digitalization%2C-Global-Business-Services-Kual/1214346166/; https://www.linkedin.com/jobs/view/senior-manager-group-internal-audit-technology-at-singtel-4275318379; https://groupcareers.singtel.com/job/Senior-manager-Group-Internal-Audit%2C-Technology-Sing/1212796366/; https://www.linkedin.com/jobs/view/senior-lead-architect-ai-ml-at-singtel-4268657194; https://groupcareers.singtel.com/job/Lead-Architect-AIML-Sing/1212284066/; https://www.linkedin.com/jobs/view/retail-executive-at-singtel-3751238362; https://groupcareers.singtel.com/job/Retail-Executive-Sing/581562710/; https://www.linkedin.com/jobs/view/product-manager-at-singtel-4427588200; https://www.linkedin.com/jobs/view/product-manager-at-singtel-4427586233; https://www.linkedin.com/jobs/view/lead-software-engineer-java-microservices-bss-cpq-at-singtel-4427160994</t>
+          <t>https://www.linkedin.com/jobs/view/industrial-postgraduate-programme-ipp-at-sea-4224374943; https://career.sea.com/position/J00216226?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/facility-engineer-at-sea-4127956136; https://career.sea.com/position/J01988208?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/product-management-s-r-a-c-regional-trust-safety-sea-labs-at-sea-4335970537; https://id.indeed.com/viewjob?jk=6dd0c2f8e5d8ac9c; https://career.sea.com/position/J02076684; https://www.linkedin.com/jobs/view/senior-back-end-engineer-enterprise-efficiency-sea-labs-at-sea-4261955005; https://career.sea.com/position/J00281508?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/it-helpdesk-engineer-corporate-it-at-sea-4265068118; https://sg.indeed.com/viewjob?jk=d2ed4321ea3a2c9a; https://www.glassdoor.co.uk/job-listing/concierge-sea-singapore-JV_KO0,9_KE10,23.htm?jl=1009579614676; https://career.sea.com/position/J00261948; https://www.linkedin.com/jobs/view/research-intern-at-sea-3787623265; https://career.sea.com/position/J00290392?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/labs-bootcamp-program-at-sea-3740022960; https://career.sea.com/position/J00242999?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/concierge-at-sea-3699433907; https://career.sea.com/position/J00261948?source=LINKEDIN&amp;channel=10003; https://www.linkedin.com/jobs/view/assistant-manager-manager-people-strategy-at-sea-3642843633; https://career.sea.com/position/J00246182?source=LINKEDIN&amp;channel=10003</t>
         </is>
       </c>
     </row>
